--- a/data/Event_Data_NNB03VB-01.xlsx
+++ b/data/Event_Data_NNB03VB-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-09-2569 12:48</t>
+          <t>15-10-2569 06:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,19 +463,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T/L สายลีดเข้า D/F ป้องกันหม้อแปลง PEA บริเวณ ถ.ราชวงศ์ อาร์คขาดเฟส B ห่าง สถานีฯ 7 กม.</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22-09-2569 05:26</t>
+          <t>25-09-2569 12:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,19 +485,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L สายลีดเข้า D/F ป้องกันหม้อแปลง PEA บริเวณ ถ.ราชวงศ์ อาร์คขาดเฟส B ห่าง สถานีฯ 7 กม.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01-08-2569 19:21</t>
+          <t>22-09-2569 05:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,19 +507,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T/L,หม้อแปลงระบบจำหน่ายอาร์คชำรุด หน้าโรงแรมเวลาดี ห่าง 7 กม., จ่ายไฟ, 19.24</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16-06-2569 01:55</t>
+          <t>01-08-2569 19:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,19 +529,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L,หม้อแปลงระบบจำหน่ายอาร์คชำรุด หน้าโรงแรมเวลาดี ห่าง 7 กม., จ่ายไฟ, 19.24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10-06-2569 18:12</t>
+          <t>16-06-2569 01:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -556,14 +556,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07-06-2569 06:24</t>
+          <t>10-06-2569 18:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08-05-2569 19:45</t>
+          <t>07-06-2569 06:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -600,14 +600,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24-04-2569 07:21</t>
+          <t>08-05-2569 19:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23-02-2569 12:04</t>
+          <t>24-04-2569 07:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28-09-2568 15:58</t>
+          <t>23-02-2569 12:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T/L HL Clamp ชำรุด เฟส B หน้า รร.เทศบาล2 ห่าง สฟฟ. 8 กม. ขนาด 50 ACSR</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02-07-2568 10:44</t>
+          <t>28-09-2568 15:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L HL Clamp ชำรุด เฟส B หน้า รร.เทศบาล2 ห่าง สฟฟ. 8 กม. ขนาด 50 ACSR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30-07-2567 06:30</t>
+          <t>02-07-2568 10:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>27-07-2567 05:50</t>
+          <t>30-07-2567 06:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -739,20 +739,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>27-07-2567 05:50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NNB03VB-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>T/R ไม่ทราบสาเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>04-06-2567 19:56</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NNB03VB-01</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>T/R</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NNB03VB-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
